--- a/artfynd/A 54239-2025 artfynd.xlsx
+++ b/artfynd/A 54239-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>130116672</v>
       </c>
       <c r="B3" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54239-2025 artfynd.xlsx
+++ b/artfynd/A 54239-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130111838</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>130116672</v>
       </c>
       <c r="B3" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54239-2025 artfynd.xlsx
+++ b/artfynd/A 54239-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>130116672</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54239-2025 artfynd.xlsx
+++ b/artfynd/A 54239-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130111838</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>130116672</v>
       </c>
       <c r="B3" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54239-2025 artfynd.xlsx
+++ b/artfynd/A 54239-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130111838</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54239-2025 artfynd.xlsx
+++ b/artfynd/A 54239-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130111838</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54239-2025 artfynd.xlsx
+++ b/artfynd/A 54239-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130111838</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54239-2025 artfynd.xlsx
+++ b/artfynd/A 54239-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130111838</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54239-2025 artfynd.xlsx
+++ b/artfynd/A 54239-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130111838</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
